--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N92_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N92_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.53365552670737</v>
+        <v>6.424219023089948</v>
       </c>
       <c r="D2" t="n">
-        <v>40.04416791566572</v>
+        <v>6.507177286295679</v>
       </c>
       <c r="E2" t="n">
-        <v>11.52400498763737</v>
+        <v>1.872650810491073</v>
       </c>
       <c r="F2" t="n">
-        <v>11.58150083534602</v>
+        <v>1.881993885743728</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.22202012393959</v>
+        <v>6.373578270140183</v>
       </c>
       <c r="D3" t="n">
-        <v>39.76332053716715</v>
+        <v>6.461539587289662</v>
       </c>
       <c r="E3" t="n">
-        <v>11.52400498763737</v>
+        <v>1.872650810491073</v>
       </c>
       <c r="F3" t="n">
-        <v>11.58150083534602</v>
+        <v>1.881993885743728</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.18394753746194</v>
+        <v>3.767391474837565</v>
       </c>
       <c r="D4" t="n">
-        <v>23.68259954814792</v>
+        <v>3.848422426574037</v>
       </c>
       <c r="E4" t="n">
-        <v>11.52400498763737</v>
+        <v>1.872650810491073</v>
       </c>
       <c r="F4" t="n">
-        <v>11.58150083534602</v>
+        <v>1.881993885743728</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.0239080148704</v>
+        <v>3.416385052416441</v>
       </c>
       <c r="D5" t="n">
-        <v>21.12464879149725</v>
+        <v>3.432755428618303</v>
       </c>
       <c r="E5" t="n">
-        <v>11.52400498763737</v>
+        <v>1.872650810491073</v>
       </c>
       <c r="F5" t="n">
-        <v>11.58150083534602</v>
+        <v>1.881993885743728</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.59533982207135</v>
+        <v>6.921742721086594</v>
       </c>
       <c r="D6" t="n">
-        <v>43.09453891427413</v>
+        <v>7.002862573569547</v>
       </c>
       <c r="E6" t="n">
-        <v>11.52400498763737</v>
+        <v>1.872650810491073</v>
       </c>
       <c r="F6" t="n">
-        <v>11.58150083534602</v>
+        <v>1.881993885743728</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>53.50807648882031</v>
+        <v>8.695062429433301</v>
       </c>
       <c r="D7" t="n">
-        <v>53.18734220320411</v>
+        <v>8.642943108020669</v>
       </c>
       <c r="E7" t="n">
-        <v>11.52400498763737</v>
+        <v>1.872650810491073</v>
       </c>
       <c r="F7" t="n">
-        <v>11.58150083534602</v>
+        <v>1.881993885743728</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>23.62316746079676</v>
+        <v>3.838764712379474</v>
       </c>
       <c r="D8" t="n">
-        <v>24.12110004628338</v>
+        <v>3.919678757521049</v>
       </c>
       <c r="E8" t="n">
-        <v>11.52400498763737</v>
+        <v>1.872650810491073</v>
       </c>
       <c r="F8" t="n">
-        <v>11.58150083534602</v>
+        <v>1.881993885743728</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>8.368017418973945</v>
+        <v>1.359802830583266</v>
       </c>
       <c r="D9" t="n">
-        <v>8.169463987744798</v>
+        <v>1.32753789800853</v>
       </c>
       <c r="E9" t="n">
-        <v>11.52400498763737</v>
+        <v>1.872650810491073</v>
       </c>
       <c r="F9" t="n">
-        <v>11.58150083534602</v>
+        <v>1.881993885743728</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.71497051140024</v>
+        <v>6.453682708102539</v>
       </c>
       <c r="D10" t="n">
-        <v>39.31108654241712</v>
+        <v>6.388051563142783</v>
       </c>
       <c r="E10" t="n">
-        <v>11.52400498763737</v>
+        <v>1.872650810491073</v>
       </c>
       <c r="F10" t="n">
-        <v>11.58150083534602</v>
+        <v>1.881993885743728</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>42.58840622891021</v>
+        <v>6.920616012197909</v>
       </c>
       <c r="D11" t="n">
-        <v>42.95176246054246</v>
+        <v>6.97966139983815</v>
       </c>
       <c r="E11" t="n">
-        <v>11.52400498763737</v>
+        <v>1.872650810491073</v>
       </c>
       <c r="F11" t="n">
-        <v>11.58150083534602</v>
+        <v>1.881993885743728</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>32.49419498350594</v>
+        <v>5.280306684819716</v>
       </c>
       <c r="D12" t="n">
-        <v>32.775841119021</v>
+        <v>5.326074181840913</v>
       </c>
       <c r="E12" t="n">
-        <v>11.52400498763737</v>
+        <v>1.872650810491073</v>
       </c>
       <c r="F12" t="n">
-        <v>11.58150083534602</v>
+        <v>1.881993885743728</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>23.03093308130376</v>
+        <v>3.742526625711862</v>
       </c>
       <c r="D13" t="n">
-        <v>22.49826924556399</v>
+        <v>3.655968752404148</v>
       </c>
       <c r="E13" t="n">
-        <v>11.52400498763737</v>
+        <v>1.872650810491073</v>
       </c>
       <c r="F13" t="n">
-        <v>11.58150083534602</v>
+        <v>1.881993885743728</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>24.33702909884518</v>
+        <v>3.954767228562342</v>
       </c>
       <c r="D14" t="n">
-        <v>24.09938127118514</v>
+        <v>3.916149456567586</v>
       </c>
       <c r="E14" t="n">
-        <v>11.52400498763737</v>
+        <v>1.872650810491073</v>
       </c>
       <c r="F14" t="n">
-        <v>11.58150083534602</v>
+        <v>1.881993885743728</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>38.19822594387094</v>
+        <v>6.207211715879029</v>
       </c>
       <c r="D15" t="n">
-        <v>38.20916661595138</v>
+        <v>6.2089895750921</v>
       </c>
       <c r="E15" t="n">
-        <v>11.52400498763737</v>
+        <v>1.872650810491073</v>
       </c>
       <c r="F15" t="n">
-        <v>11.58150083534602</v>
+        <v>1.881993885743728</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
